--- a/Project_CNN/Main/Results/Experimento 16 - ResNet/training_metrics.xlsx
+++ b/Project_CNN/Main/Results/Experimento 16 - ResNet/training_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marci_wawp\Desktop\Arquivos\Mestrado\Projeto-Classificadores\Project_CNN\Main\Results\Experimento 16 - ResNet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7B4545-9D0E-44C3-B42C-2ED5EE4823D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90C8661-1D2A-4D6B-B1EE-C097D2EFBBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,7 +169,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6548,7 +6548,7062 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="0" baseline="0"/>
+              <a:t>Accuracy curve: ResNet-50, Batch size = 32</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1600" b="0"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$B$2:$B$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>0.44562861323357</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.46957072615623002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.47880819439888</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.49284550547599998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.50072449445723999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.51041477918625</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52209746837616</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.51231658458710005</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.51720702648162997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.54419487714767001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.56855642795562999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.57118272781372004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.58675962686538996</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.60278934240340998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.60034412145615001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.60885709524154996</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.61800396442412997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.62778484821320002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.62035864591598999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.63512045145035001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.63702225685119995</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.64164102077483998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.64825212955474998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.64444845914840998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.64879548549652</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.67370039224625</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.66564029455185003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.67587393522262995</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.68185108900070002</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.68302845954894997</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.71490669250488004</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.72242349386214999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.72568374872207997</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.73492121696472001</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.74026441574097002</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.73745697736740001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.74044555425643999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.73872488737106001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.73953992128372004</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.74397754669188998</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.74660384654999001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.74551713466643998</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.74895852804184004</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.74968302249908003</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.74796229600905995</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.75412064790725997</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.75022643804550004</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.76525992155074996</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.75520741939545</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.75339615345000999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.75964498519896995</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.76734286546706998</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.75864881277083995</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.76381093263625999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.76580327749251997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.76525992155074996</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.76842963695526001</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.76489764451981002</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.76761454343795998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.77531242370605002</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.77830106019973999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.78536498546599998</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.77911609411240001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.78011232614517001</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.78228580951690996</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.77793878316878995</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.78464049100875999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.78536498546599998</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.78536498546599998</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.78427821397780995</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.78255748748778997</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.78916865587233997</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.78138017654419001</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.77911609411240001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.78636115789412997</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.78880637884140004</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.78545552492142001</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.78790074586867997</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.78654229640961004</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.78735738992690996</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.79242891073226995</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.78608947992324996</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.79061764478683005</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.78726679086685003</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.79161381721497004</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.79170441627501997</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.78907805681229004</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.78898751735687001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.79270058870315996</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.78708565235137995</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.78636115789412997</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.79424017667769997</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.78527438640594005</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.79233837127686002</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.79125159978866999</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.78889691829680997</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.79704761505126998</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.79523634910582996</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.79351568222045998</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.79070818424224998</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.79261004924774003</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.78726679086685003</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.78934973478317005</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.79224777221679998</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.79061764478683005</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.78708565235137995</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.79070818424224998</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.78726679086685003</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.79460245370865001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.79469299316405995</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.79623258113860995</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.79496467113494995</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.79279118776321</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.79007428884506004</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.79596090316771995</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.79532694816589</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.79414963722229004</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.78944033384322998</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.79931169748305997</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.79487413167953003</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.79125159978866999</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.79759103059768999</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.80021733045578003</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.79161381721497004</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.80284368991851995</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.79523634910582996</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.79677593708037997</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.79650425910949996</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.79315340518951005</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.79387789964676003</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.78799128532410001</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.79985511302947998</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.79922115802765004</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.79487413167953003</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.80329650640488004</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.79768157005310003</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.79659479856491</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.79686653614044001</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.79822498559952004</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.79704761505126998</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.79949283599854004</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.80230033397675005</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.79840606451035001</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.79768157005310003</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.79740989208221003</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.80085128545760997</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.8019380569458</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.79587030410767001</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.80257201194762995</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.79505527019500999</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.8019380569458</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.80519831180572998</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.79904001951217996</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.80166637897491</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.80057960748671997</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.80347764492035001</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.79740989208221003</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.80338704586028997</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.80728131532669001</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.79804384708404996</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.80157577991485995</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.80220973491669001</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.80184751749038996</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.79994565248489002</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.80420213937759</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.80619454383849998</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.80610394477844005</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.80257201194762995</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.80863976478577004</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.79967397451401001</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.80048906803131004</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.80266255140304998</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.80474549531937001</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.80057960748671997</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.80764353275298995</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.80601340532303001</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.80537945032119995</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.80637568235396995</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.80655676126480003</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.80356818437576005</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.80338704586028997</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.81316792964935003</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.80411159992217995</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.81036043167114002</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.80755299329758001</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.80275315046310003</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.80601340532303001</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.81054157018660999</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.80474549531937001</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.80764353275298995</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.81117552518845004</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.80818694829940996</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.81153774261474998</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.80664736032485995</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.80918312072753995</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.80755299329758001</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.81090384721756004</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.80945479869842996</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.80646622180938998</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.81162834167480002</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.80900198221206998</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.81153774261474998</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.80854916572571001</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.81733381748198997</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.80854916572571001</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.81470745801926003</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.81307733058928999</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.81796777248383001</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.80610394477844005</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.80574172735214</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.81452637910842995</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.81651872396469005</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.81199055910109996</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.81054157018660999</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.81443578004837003</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.81380182504653997</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.81298679113387995</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.81262451410294001</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.81497919559479004</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.81660932302474998</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.81416410207748002</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.81950736045837003</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.81380182504653997</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.81162834167480002</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.81452637910842995</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.81171888113021995</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.81814891099929998</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.81307733058928999</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.81235283613205</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.81996017694473</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.82168084383010997</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.81851112842560003</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.82376378774643</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.82213366031646995</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.81516027450562001</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.81642818450928001</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.81796777248383001</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.81832998991012995</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.80981707572937001</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.82086580991744995</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.81733381748198997</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.82014125585555997</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.82140916585921997</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.82312989234924006</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.81778663396835005</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.81570369005203003</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.82367324829101995</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.82349210977553999</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.81597536802292003</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.82068467140197998</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.81887340545653997</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.82059407234191994</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.82005071640015004</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.81959789991378995</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.82086580991744995</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.82122802734375</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.82322043180465998</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.81851112842560003</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.81742435693741</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.82430720329285001</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.82186198234558006</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.82023185491562001</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.82521283626555997</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.81959789991378995</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.82584679126740002</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.81642818450928001</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.82159030437469005</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.81986957788466996</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.82186198234558006</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.82593733072280995</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.82611846923828003</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.82349210977553999</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.82331097126007002</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.82548451423644997</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.82041299343108998</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.82403552532196001</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.82892590761185003</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.82412606477737005</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.82485055923462003</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.82847309112548995</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.82557505369186002</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.83073717355728005</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.83300125598907004</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.82476001977920999</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.82222425937652999</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.82702410221099998</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.82557505369186002</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.83064663410187001</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.82512223720551003</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.82838255167007002</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.82684296369553001</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.82883536815643</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.83028435707091996</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.82874476909636996</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.83064663410187001</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.83091831207275002</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.82639014720917003</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.83263903856277</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.83164280653</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.82955986261367998</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.82693350315094005</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.83762001991271995</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.83200508356094005</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.83254843950271995</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.82874476909636996</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.83254843950271995</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.83354467153548994</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.82928818464278997</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.83598983287811002</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.82865422964096003</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.83517479896544999</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.83499366044998002</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.83562761545180997</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.83073717355728005</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.82838255167007002</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.82992213964462003</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.83128058910369995</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.83182394504546997</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.83236730098723999</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.82965040206909002</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.83118999004364003</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.83082777261733998</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.83490312099456998</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.83399748802185003</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.83481252193451005</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.82783913612366</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.83970296382903997</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.83336353302001998</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.82955986261367998</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.83997464179992998</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.83934068679810003</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.83282011747359996</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.83553701639175004</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.83490312099456998</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.83571815490723</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.83888787031173995</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.83200508356094005</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.83309185504912997</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.84205758571625</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.83653324842453003</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.84205758571625</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.83463138341903997</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.82820141315460005</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.83725774288177002</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.83825391530991</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.83499366044998002</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.83834451436996005</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.83878248929976995</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.83291071653366</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.83626157045364002</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.83644264936446999</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.83897846937179998</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.84350663423537997</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.84106141328812001</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.83861619234085005</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.83870673179625999</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.83780109882355003</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.83743888139724998</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.84386885166168002</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.84368771314621005</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.83897846937179998</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.83807283639908003</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.83879733085632002</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.84513676166534002</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.84187644720078003</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.83861619234085005</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.84260100126266002</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.83915954828261996</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.83925014734268</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.83906900882721003</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.84558957815169999</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.85229122638702004</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.84432166814803999</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.84260100126266002</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.84015578031539995</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.84350663423537997</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.84332549571991</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.84124255180358998</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.84459334611893</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.84749138355255005</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.84459334611893</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.84658575057982999</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.83943128585814997</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.84866869449615001</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.85120451450348</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.85029888153076005</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.84948378801346003</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.84377831220626998</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.84251040220260998</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.84812533855437999</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.84821587800980003</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.84622353315353005</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.85355913639069003</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.84930264949798995</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.84830647706984996</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.85211014747619995</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.84749138355255005</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.84350663423537997</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.85002714395523005</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.85138559341430997</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.84577071666717996</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.84667634963989002</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.84767252206802002</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.84948378801346003</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.8524723649025</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.85319685935973999</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.84984606504439997</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.85111391544341997</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.85120451450348</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.85573267936706998</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.84884983301162997</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.84939324855803999</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.85355913639069003</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.84432166814803999</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.84866869449615001</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.85084223747252996</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.85029888153076005</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.85020828247070002</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.84939324855803999</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.85147619247437001</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.85002714395523005</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.85392141342162997</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.85437422990798995</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.85038942098617998</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.85310631990432995</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.85690999031066994</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.85111391544341997</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.85337799787520996</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.85111391544341997</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.85428363084793002</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.85763448476791004</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.85446476936339999</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.85301578044891002</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.85066109895705999</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.85600435733794999</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.85935521125793002</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.85310631990432995</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.85075169801712003</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.85736280679703003</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.85890239477158004</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.85808730125427002</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.85600435733794999</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.85183840990066995</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.85700052976607999</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.85627603530884</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.85908347368240001</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.84984606504439997</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.85944575071335005</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.85835897922516002</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.85681939125061002</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.86017024517059004</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.86107587814330999</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.85781562328339001</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.85491758584975996</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.85899293422698997</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.85826843976973999</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.85935521125793002</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.85826843976973999</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.86053252220153997</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.86035138368607</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.86089473962784002</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.85926461219787997</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.86406445503234997</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.86424559354782005</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.86116647720337003</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.85926461219787997</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.85681939125061002</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.86243432760239003</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.85591375827788996</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.85555154085159002</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.86261546611786</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.85854011774062999</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.86180037260055997</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.86243432760239003</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.86533236503600997</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.86669081449509</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.86198151111603005</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.86370223760605003</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.86243432760239003</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.86026084423064997</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.85917407274246005</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.86270600557327004</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.86333996057509999</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.86116647720337003</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.86370223760605003</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.86696249246597001</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.86397391557693004</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.86089473962784002</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.86352109909057995</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.86007970571518</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.86578518152237005</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.86315882205963002</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.86406445503234997</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.86234378814696999</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.86406445503234997</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.86723417043686002</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.86225318908690995</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.87185293436050004</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.86397391557693004</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.86786812543868996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C50C-49C7-9147-543FBA4ED46E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_accuracy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$E$2:$E$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>0.38481104373932001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.47274708747864003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.50690406560898005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.54905521869659002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.53888082504271995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.54069769382476995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.56795060634613004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.57376456260680997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.58284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.56686043739319003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.58975291252135997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.58793604373931996</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.64280521869659002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.64716571569443004</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.64898258447646995</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.67223834991455</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.61555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.67805230617523005</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.67768895626068004</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.67005813121795998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.65479654073714999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.63117730617523005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.69258719682693004</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.63553780317306996</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.69513082504271995</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.71802324056625</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.71620637178420998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.72492730617523005</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.73074126243590998</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.71765989065169999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.75581395626068004</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.75835758447646995</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.75436043739319003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.76998543739319003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.76853197813034002</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.77180230617523005</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.76816862821579002</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.77252906560898005</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.78561043739319003</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.78670060634613004</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.77725291252135997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.78379362821579002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.78524708747864003</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.79069769382476995</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.77688956260680997</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.79832845926285001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.78015989065169999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.78815406560898005</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.78960758447646995</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.77616280317306996</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.78015989065169999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.80268895626068004</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.79578489065169999</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.79941862821579002</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.78052324056625</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.79215115308761996</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.81104654073714999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.80523258447646995</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.81031978130340998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.80050873756409002</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.81140989065169999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.80886626243590998</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.81213665008545</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.81322675943375</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.81904071569443004</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.82303780317306996</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.81104654073714999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.81758719682693004</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.81322675943375</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.81649708747864003</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.81504362821579002</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.8125</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.81468021869659002</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.81359010934830001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.82376456260680997</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.82194769382476995</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.81867730617523005</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.81613373756409002</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.80777615308761996</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.81722384691238004</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.81795060634613004</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.82231104373931996</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.81649708747864003</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.82194769382476995</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.81722384691238004</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.81795060634613004</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.81831395626068004</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.81867730617523005</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.81431686878204002</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.82485467195510997</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.82158428430556996</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.81613373756409002</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.82231104373931996</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.82558137178420998</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.81577032804489003</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.82085758447646995</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.82158428430556996</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.82412791252135997</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.82303780317306996</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.82485467195510997</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.81177324056625</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.82340115308761996</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.82303780317306996</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.81831395626068004</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.82449126243590998</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.82630813121795998</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.82630813121795998</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.82776165008545</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.82667154073714999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.82231104373931996</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.81722384691238004</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.82957845926285001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.82558137178420998</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.82558137178420998</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.82485467195510997</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.82340115308761996</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.82340115308761996</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.82122093439101995</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.828125</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.82158428430556996</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.82703489065169999</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.82231104373931996</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.82667154073714999</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.82594478130340998</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.82412791252135997</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.82449126243590998</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.82594478130340998</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.81758719682693004</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.828125</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.82703489065169999</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.82412791252135997</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.82776165008545</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.82303780317306996</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.82340115308761996</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.82957845926285001</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.82848834991455</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.82776165008545</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.82667154073714999</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.83066862821579002</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.82667154073714999</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.82594478130340998</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.83103197813034002</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.83030521869659002</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.82776165008545</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.82667154073714999</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.83030521869659002</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.82957845926285001</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.83139532804489003</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.82994186878204002</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.82739824056625</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.83103197813034002</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.82013082504271995</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.83321219682693004</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.83248543739319003</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.82848834991455</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.82739824056625</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.82848834991455</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.82376456260680997</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.81359010934830001</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.82885175943375</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.82957845926285001</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.83103197813034002</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.828125</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.82594478130340998</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.82340115308761996</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.83030521869659002</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.83066862821579002</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.83175873756409002</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.81976741552353005</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.83539241552353005</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.82776165008545</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.83393895626068004</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.83103197813034002</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.83430230617523005</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.83175873756409002</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.83430230617523005</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.828125</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.83284884691238004</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.83248543739319003</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.82303780317306996</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.83684593439101995</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.82667154073714999</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.83175873756409002</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.82122093439101995</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.83357560634613004</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.82412791252135997</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.83466571569443004</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.83212208747864003</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.83502906560898005</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.83212208747864003</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.83066862821579002</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.83175873756409002</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.83248543739319003</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.83139532804489003</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.83030521869659002</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.83611917495728005</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.83357560634613004</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.83793604373931996</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.83502906560898005</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.83502906560898005</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.83139532804489003</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.83720928430556996</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.83648258447646995</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.83393895626068004</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.83611917495728005</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.84193313121795998</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.83575582504271995</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.82158428430556996</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.83757269382476995</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.83684593439101995</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.84411334991455</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.83829939365386996</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.83357560634613004</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>0.82303780317306996</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>0.84193313121795998</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>0.83829939365386996</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.83248543739319003</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>0.84084302186965998</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>0.84629362821579002</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>0.83393895626068004</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>0.84229654073714999</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.84193313121795998</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>0.83866280317306996</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>0.84084302186965998</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>0.83902615308761996</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>0.84265989065169999</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.84193313121795998</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>0.83829939365386996</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.84484010934830001</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.84302324056625</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>0.84520345926285001</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.84229654073714999</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.83684593439101995</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>0.84411334991455</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.84229654073714999</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>0.84375</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>0.84556686878204002</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>0.84156978130340998</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.84702032804489003</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>0.84484010934830001</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>0.84556686878204002</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>0.85065406560898005</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>0.82921510934830001</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>0.84992730617523005</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>0.84338665008545</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>0.83938956260680997</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>0.84120637178420998</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.83829939365386996</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>0.83466571569443004</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>0.84593021869659002</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>0.84447675943375</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>0.84738373756409002</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>0.84847384691238004</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>0.84920060634613004</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>0.83466571569443004</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>0.84193313121795998</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>0.84411334991455</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>0.84556686878204002</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>0.85029071569443004</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>0.83175873756409002</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>0.85428780317306996</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>0.84011626243590998</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>0.84665697813034002</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>0.84774708747864003</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.85501456260680997</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>0.85210758447646995</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>0.83793604373931996</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.85755813121795998</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>0.84956395626068004</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>0.85792154073714999</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>0.85646802186965998</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.85319769382476995</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>0.85610467195510997</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>0.85465115308761996</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>0.85138082504271995</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>0.84520345926285001</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>0.85973834991455</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>0.85973834991455</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>0.84556686878204002</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>0.85283428430556996</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>0.85537791252135997</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>0.86191862821579002</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>0.86264532804489003</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>0.84556686878204002</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>0.86155521869659002</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>0.86300873756409002</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.86373543739319003</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.85683137178420998</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.85864824056625</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.87027615308761996</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>0.86700582504271995</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>0.85101741552353005</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>0.86119186878204002</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>0.85719478130340998</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0.859375</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>0.86409884691238004</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>0.85392439365386996</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>0.84811043739319003</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>0.86010175943375</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>0.86337208747864003</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>0.85247093439101995</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>0.86082845926285001</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>0.86664241552353005</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>0.86773258447646995</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>0.84883719682693004</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>0.85828489065169999</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>0.86845928430556996</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>0.86809593439101995</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>0.87427324056625</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>0.87463665008545</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0.87136626243590998</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.87245637178420998</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>0.85901165008545</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.86555230617523005</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>0.85174417495728005</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>0.86046510934830001</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>0.86736917495728005</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.86482560634613004</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>0.86228197813034002</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>0.86882269382476995</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>0.86918604373931996</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>0.87172967195510997</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>0.86518895626068004</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>0.87209302186965998</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>0.87318313121795998</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.87063956260680997</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>0.86954939365386996</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>0.86627906560898005</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>0.86591571569443004</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>0.86446219682693004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C50C-49C7-9147-543FBA4ED46E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="393590320"/>
+        <c:axId val="393592720"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="393590320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="499"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0"/>
+                  <a:t>Epochs</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1400" b="0"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393592720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="393592720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0"/>
+                  <a:t>Accuracy</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1600" b="1" baseline="0"/>
+                  <a:t> (%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1600" b="1"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="393590320"/>
+        <c:crossesAt val="1"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Loss curve: ResNet-50, Batch size = 32</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$C$2:$C$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>2.8178787231445002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7852089405060001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.7549321651458998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.7238907814025999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6919124126434002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.6564283370971999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.6261816024779998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.6107594966888001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5747432708739999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.5250256061553999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4732196331024001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.4489991664885999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.4073460102081001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.3637120723724001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3288755416870002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.2957601547241002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2602140903472998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.2158730030060001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.2091195583343999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.1627783775329998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.1384918689728001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.1088697910309002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.0872607231139999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.0649406909943</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.0412530899047998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.9944652318953999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.978067278862</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.9446167945862001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.9239907264709</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.9175673723221001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.8353599309921</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.816407084465</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.8085510730743</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.7974447011948</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.7901639938353999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.7902989387512001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.7824214696884</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.7717919349669999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.7749929428100999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.7675368785858001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.7620010375977</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.7625007629395</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.7558158636093</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.7510161399841</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.7451525926589999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.7350656986237001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.7404427528380999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.7255162000655999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.7328957319260001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.7334215641021999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.7138453722</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.7064718008041</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.7132554054260001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1.7110421657562001</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.7090750932693</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.7065522670746001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.6979657411575</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.6944836378098</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.6976934671402</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.6857016086578001</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.6680408716202</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.6624509096146001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.6614589691162001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1.6605433225632</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1.6587275266646999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1.6574912071228001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1.6564382314682</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1.6561698913573999</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1.65662586689</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1.6523609161377</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1.6539885997771999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1.6462970972061</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1.6590754985809</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1.6617349386214999</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1.6525961160660001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1.6435060501098999</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1.6571559906005999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1.6515175104141</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>1.6505061388016</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1.6491193771362</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1.6451700925827</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1.6508941650391</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1.6473339796066</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1.6504203081130999</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>1.6439784765244001</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1.6411021947861</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1.644015789032</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>1.6431028842926001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1.6406308412552</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1.6426794528961</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1.6436421871185001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1.6440492868423</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1.6394313573837</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1.6434420347214</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1.6410173177719001</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1.6453622579575</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1.6300503015518</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1.6287490129471001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1.6374763250351001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1.6370408535004</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1.6405881643294999</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1.6451644897461</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1.6355196237564</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1.6291390657425</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1.6368346214294001</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1.6382502317429</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1.6392444372177</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1.636345744133</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1.6301913261414001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1.6294887065887</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1.6315957307816</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1.6328030824661</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1.6309490203857</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1.6363914012909</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1.6261378526688</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1.6286648511887001</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>1.6329210996628001</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>1.6333403587341</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>1.6242415904998999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1.6278705596923999</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>1.6283041238785001</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>1.6193463802338</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>1.6149652004242001</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>1.6318264007568</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>1.6156011819839</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>1.6211928129196</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>1.6232957839966</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>1.6214261054993</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>1.6298993825912</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>1.6243261098862001</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>1.6322411298752</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1.61514544487</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>1.6226823329925999</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>1.6176741123199001</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>1.612931728363</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>1.6234743595123</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>1.6169093847275</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>1.6257598400116</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>1.6155035495757999</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>1.6206525564194001</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1.6132264137268</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1.6093348264694001</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1.6214575767517001</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>1.6202590465546001</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>1.6164274215698</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>1.6152876615523999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>1.6124854087830001</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>1.6179422140121</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>1.6140506267548</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>1.6121068000793</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>1.6115821599960001</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>1.6032871007919001</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>1.6098281145096001</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>1.6091673374176001</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>1.6037453413010001</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>1.6053181886673</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>1.6140695810318</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>1.6090170145035001</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>1.5998821258545</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>1.6121846437453999</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>1.6076111793518</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>1.6014969348907</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>1.6054131984711</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>1.6029394865036</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1.6015368700027</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1.600946187973</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1.6002392768860001</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1.6042288541794001</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1.5965597629546999</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1.6106762886046999</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1.6047301292419001</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1.6039719581603999</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1.6024421453476001</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1.6033017635344999</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1.5976854562759</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1.5968058109283001</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1.59708070755</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1.5953074693680001</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1.5970296859741</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1.6003446578978999</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1.6009202003478999</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1.5865178108214999</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1.5969848632812</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1.5869978666305999</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1.5913826227187999</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1.5966376066207999</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1.5981916189194001</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1.5905891656875999</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1.5913021564484</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1.5896803140639999</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1.5883073806763</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1.5899672508239999</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1.5831149816512999</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1.5905270576477</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1.5885000228882</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1.5878711938857999</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1.5826034545898</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1.5869772434235001</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1.5856871604919001</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1.5801596641541</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1.5891215801239</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>1.5837093591689999</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>1.5848921537398999</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1.573414683342</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>1.5924775600433001</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>1.5726959705353001</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>1.5800178050995</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>1.5745105743408001</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>1.5846775770187</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>1.5895553827286</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>1.5818430185318</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>1.5783458948135001</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>1.5804934501648</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>1.5790675878525</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>1.5761878490448</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>1.5745491981505999</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>1.5743175745010001</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>1.5792669057846001</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>1.5755290985107</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>1.5727792978287001</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>1.5741083621979</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>1.5657875537871999</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>1.5688781738280999</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>1.5737873315811</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>1.5738049745560001</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>1.5727953910828001</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>1.5662873983383001</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>1.5760413408278999</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>1.5746695995330999</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>1.5616499185562001</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>1.5634390115737999</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>1.5701304674148999</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>1.5637730360030999</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>1.5584614276886</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>1.5740154981612999</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>1.5648658275603999</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>1.5655682086945</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>1.5649895668030001</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>1.5716842412948999</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>1.5580933094025</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>1.5650707483291999</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>1.5581487417221001</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>1.5578083992003999</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>1.5569984912871999</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>1.5612134933471999</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>1.5599802732468</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>1.5523647069930999</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>1.5530532598494999</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>1.5634893178939999</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>1.556223154068</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>1.5579059123993</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>1.5615386962891</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>1.5559043884277</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>1.5627865791321001</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>1.5560275316237999</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>1.5484018325805999</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>1.5491640567780001</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>1.5572712421417001</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>1.5549817085266</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>1.5474193096161</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>1.5545879602432</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>1.5547747612</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>1.5492185354232999</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>1.5535014867782999</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>1.5410528182983001</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>1.5554710626602</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>1.5513099431991999</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>1.5491362810135001</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>1.5513991117477</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>1.5441865921021001</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>1.5404641628264999</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>1.5453479290009</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>1.5472567081451001</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>1.5405617952346999</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>1.5478668212891</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>1.5496832132339</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>1.5370798110962001</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>1.5465477705002</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>1.546858549118</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>1.5358260869980001</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>1.5428013801575</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>1.5368465185164999</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>1.535427570343</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>1.5438243150711</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>1.5421688556671</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>1.5367692708969001</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>1.5406411886214999</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>1.5307509899139</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>1.5452595949173</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>1.5392917394637999</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>1.5381934642791999</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>1.5342619419098</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>1.5320961475371999</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>1.5310480594635001</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>1.5313498973846</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>1.5366469621658001</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>1.5343503952026001</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>1.5278236865996999</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>1.5268833637238</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>1.5324050188064999</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>1.5291923284530999</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>1.5243003368378001</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>1.5342199802398999</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>1.5241566896439001</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>1.5328624248505001</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>1.5295530557632</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>1.5219955444336</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>1.5308475494385001</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>1.5220996141434</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>1.5343343019485001</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>1.5258029699325999</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>1.5233315229416</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>1.5174885988235001</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>1.5239986181259</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>1.5326923131943</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>1.5215666294098</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>1.523411154747</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>1.5177882909775</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>1.5241110324860001</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>1.5256534814835001</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>1.5294753313064999</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>1.5217845439911</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>1.5171707868576001</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>1.5205161571503001</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>1.5216737985611</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>1.5250333547592001</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>1.510859131813</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>1.5149818658829</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>1.5198402404785001</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>1.5086116790771</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>1.5084544420242001</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>1.5151489973068</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>1.5122642517089999</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>1.5173163414001001</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>1.5127848386764999</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>1.5123429298401001</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>1.5147218704223999</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>1.5131475925446001</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>1.5074484348296999</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>1.5098690986633001</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>1.5008730888366999</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>1.510458111763</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>1.5205016136169001</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>1.5028582811355999</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>1.5097992420196999</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>1.5148898363112999</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>1.5093326568604</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>1.5009905099869001</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>1.5136460065841999</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>1.5074955224991</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>1.5087968111037999</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>1.5078414678573999</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>1.5005751848221001</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>1.4996085166930999</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>1.5063354969025</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>1.5064307451248</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>1.5074827671051001</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>1.5032134056091</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>1.4938579797745</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>1.4950985908508001</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>1.5024987459182999</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>1.5026785135269001</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>1.5016232728958001</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>1.4957519769669001</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>1.4956214427948</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>1.498601436615</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>1.4968377351761</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>1.4963741302489999</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>1.4967890977859</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>1.4996531009673999</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>1.4927418231964</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>1.480651140213</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>1.4997287988663</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>1.494656920433</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>1.4920426607132</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>1.4918549060821999</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>1.4908375740051001</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>1.4935041666030999</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>1.4913977384567001</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>1.4873247146605999</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>1.4916278123855999</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>1.4862539768219001</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>1.4949026107787999</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>1.4840074777603001</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>1.4838213920593</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>1.4785982370377</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>1.4767980575562001</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>1.4858489036560001</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>1.4924463033676001</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>1.4833511114119999</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>1.4836193323135001</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>1.4843292236328001</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>1.4768314361571999</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>1.4846580028534</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>1.4788563251494999</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>1.4760966300964</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>1.4797719717026001</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>1.4846246242523</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>1.4795310497284</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>1.4745014905930001</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>1.48037981987</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>1.483359336853</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>1.4771994352341</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>1.4767948389053001</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>1.4750624895096001</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>1.4774590730667001</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>1.4745757579803001</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>1.4745842218398999</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>1.4803179502487001</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>1.4694361686707</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>1.4742826223373</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>1.4725135564803999</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>1.4712899923325</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>1.4776868820189999</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>1.4746599197388</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>1.4703648090363</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>1.4750311374664</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>1.4703966379166</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>1.4733533859253001</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>1.472417473793</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>1.4768967628478999</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>1.465313911438</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>1.464250087738</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>1.4695109128952</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>1.4685510396957</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>1.4623217582703001</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>1.4669953584671001</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>1.4658802747726001</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>1.4649634361267001</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>1.4590116739273</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>1.4622262716293</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>1.4586846828461</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>1.4667737483978001</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>1.4611805677414</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>1.4617384672164999</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>1.4564902782439999</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>1.461031794548</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>1.4671927690505999</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>1.4576508998871001</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>1.4589995145798</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>1.4533351659775</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>1.4604886770248</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>1.4665107727051001</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>1.4561740159987999</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>1.4567694664001001</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>1.4550232887268</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>1.4623594284057999</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>1.450600028038</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>1.4540483951569001</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>1.4523189067841</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>1.4497388601303001</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>1.4524766206741</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>1.4467978477478001</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>1.4540786743164</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>1.4509798288344999</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>1.4503129720687999</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>1.447887301445</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>1.4478944540023999</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>1.4476615190505999</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>1.44766497612</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>1.4483135938644001</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>1.4462280273438</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>1.4395598173141</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>1.4468820095062001</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>1.4388399124146001</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>1.4476732015610001</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>1.4444741010666</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>1.4440603256225999</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>1.4487488269805999</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>1.4500173330307</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>1.4423384666443</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>1.4480649232864</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>1.4437342882155999</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>1.4376497268677</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>1.4391407966614</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>1.4344258308411</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>1.4415179491043</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>1.4393131732941</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>1.4397352933884</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>1.438315987587</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>1.4384932518005</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>1.4377257823944001</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>1.4389309883118</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>1.4398754835129</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>1.4386651515961</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>1.4313017129898</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>1.4374699592589999</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>1.4331380128860001</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>1.4321647882462001</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>1.4453325271605999</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>1.4340606927871999</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>1.43741106987</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>1.4270536899566999</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>1.4421035051346001</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>1.4346202611923</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>1.4287130832671999</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>1.4401208162307999</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>1.4186298847198</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>1.4325841665268</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>1.4342027902603001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4296-4AF8-B19A-703FFCA3675E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Worksheet!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>val_loss</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Worksheet!$F$2:$F$504</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="503"/>
+                <c:pt idx="0">
+                  <c:v>2.8156337738036998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.7692034244536998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.7315208911896001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.6932845115661999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.6599390506743998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.6139659881592001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.5757248401642001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5485961437225</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.5343427658081001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.4795992374420002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4113211631775</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.4318861961364999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.3131809234618999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.3321120738982999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.2430539131164999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.1996879577636999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2362022399902002</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.1272544860839999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.0996408462524001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.1017413139343</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.0797705650329998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.0816144943236998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.9983317852019999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.0463705062866002</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.9564522504807</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.9189786911011</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.8995352983475</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.8631217479705999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.8360393047332999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.8441772460938</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.7705402374268</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.7569488286971999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.7627785205841</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.7435252666473</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.7475754022598</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.7326122522353999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.7486989498137999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.7279698848724001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.7129617929459</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.709317445755</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.712763428688</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.7149360179901001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.7136006355286</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.6939885616302</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.7117065191269001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.6828434467316</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.6962192058562999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.6972945928573999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.6933281421660999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.7029899358749001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.6953618526459</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.6619147062302</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.6728744506836</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1.6662237644196001</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.6976130008698</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.6675354242325</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.6427965164185001</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.6436851024628001</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.65376496315</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.6456451416016</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.6299626827239999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.6293510198593</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.6289252042769999</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1.6273157596587999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1.6244364976882999</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1.6235717535019001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1.6264128684998</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1.6238912343979</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1.6252491474152</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1.6214674711227</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1.6238486766814999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1.6282966136932</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1.6227374076843</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1.6254634857178001</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1.6239304542541999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1.6211965084076001</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1.6243064403534</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1.624107003212</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>1.6258338689803999</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1.6192451715469001</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1.6182678937912001</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1.6181950569153001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1.6201742887496999</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1.6164983510971001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>1.6187977790832999</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1.6188342571259</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1.6178727149962999</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>1.6176700592041</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1.6210944652557</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1.6130632162094001</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1.6165474653244001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1.616826415062</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1.611200928688</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1.6119054555893</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1.6175264120102</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1.6143901348114</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1.6085767745971999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1.6091842651367001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1.6107722520828001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1.608087182045</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1.6162811517714999</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1.6076264381409</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1.6069790124893</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1.6118613481521999</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1.610123872757</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1.608513712883</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1.6067909002303999</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1.6088136434555</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1.6039912700653001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1.6032729148864999</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1.6096118688583001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1.6017642021178999</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1.6052722930908001</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1.6038619279860999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1.6046847105026001</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1.5991358757019001</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>1.602201461792</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>1.6051651239394999</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>1.5996624231339001</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1.6081488132477</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>1.5986915826796999</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>1.5995707511902</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>1.6094553470612001</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>1.6004179716110001</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>1.6002081632614</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>1.6000112295151001</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>1.5967788696289</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>1.5968064069748</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>1.6090916395187</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>1.5957517623901001</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>1.5917128324509</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1.59787940979</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>1.5980657339096001</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>1.5956196784973</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>1.5988726615905999</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>1.6003433465957999</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>1.5894746780396001</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>1.5930441617966</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>1.5906578302383001</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>1.5909696817398</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1.5908985137939</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1.5955638885498</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1.5950145721436</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>1.5879704952239999</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>1.5830012559891</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>1.5905478000641</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>1.5977222919464</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>1.5834379196167001</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>1.5913343429564999</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>1.5926669836044001</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>1.5857398509978999</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>1.5913729667664001</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>1.5876532793045</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>1.5875506401062001</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>1.591619849205</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>1.5863164663314999</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>1.5973151922226001</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>1.5823103189468</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>1.5821226835251001</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>1.583141207695</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>1.5881786346436</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>1.5872431993484</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>1.5921095609664999</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>1.5820124149323</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1.5794717073441</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1.5897076129912999</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1.6012846231461</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1.5821588039398</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1.5789570808411</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1.5790542364119999</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1.5806120634078999</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1.5868519544601001</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1.5892024040221999</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1.5884399414062</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1.585687994957</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1.5808742046355999</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1.5788377523421999</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1.576966047287</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1.5934724807739</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1.5755759477614999</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1.5886307954787999</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1.5763031244278001</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1.5798972845078001</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1.5767855644226001</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1.5763448476791</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1.5756940841675</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1.5847959518432999</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1.5761119127273999</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1.5713568925857999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1.5896660089493</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1.5697987079619999</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1.5800908803939999</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1.5779041051864999</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1.5952835083007999</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1.5733422040939</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1.5846351385116999</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1.5663158893585001</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1.5741360187530999</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1.5664490461349001</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1.5744247436523</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1.5718013048171999</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>1.5597156286239999</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>1.5763720273971999</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1.5713280439377</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>1.5678849220276001</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>1.5681691169739</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>1.5760998725891</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>1.5625213384628001</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>1.5682212114334</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>1.5620594024658001</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>1.5690121650696001</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>1.5633127689362001</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>1.5752000808716</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>1.5580105781555</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>1.5593571662903001</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>1.5549134016037001</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>1.5588040351868</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>1.5582360029221001</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>1.5671367645264001</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>1.5610507726669001</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>1.5509512424469001</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>1.5630851984023999</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>1.55615234375</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>1.5808087587357</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>1.5563026666641</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>1.5609512329102</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>1.5572731494904</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>1.5566660165787001</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>1.5531497001648</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>1.5618863105773999</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>1.5600517988205</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>1.5587255954742001</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>1.5581215620041</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>1.548711180687</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>1.5711959600448999</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>1.5596023797989</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>1.5523580312729</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>1.5442235469818</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>1.5495617389678999</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>1.5539427995682</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>1.5554562807083001</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>1.5510814189911</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>1.5493025779723999</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>1.5434173345566</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>1.5517697334289999</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>1.5444798469543</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>1.5572876930237001</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>1.5456703901291</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>1.5419834852219001</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>1.5476984977721999</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>1.5517127513885001</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>1.5457742214203001</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>1.5518718957901001</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>1.536930680275</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>1.5443130731582999</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>1.5492718219757</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>1.5367848873137999</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>1.5398643016814999</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>1.542702794075</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>1.5378738641739</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>1.5417397022246999</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>1.5368709564209</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>1.5508431196212999</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>1.5370043516159</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>1.5453072786330999</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>1.5433698892593</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>1.5327849388123</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>1.5292714834212999</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>1.5341604948044001</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>1.5297935009003001</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>1.5318664312363</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>1.5346912145614999</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>1.5289142131805</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>1.5294443368912001</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>1.5279421806335001</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>1.5282672643660999</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>1.5284459590912001</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>1.5330582857132</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>1.5462679862976001</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>1.5276931524277</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>1.5275737047194999</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>1.5238739252089999</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>1.5322040319443</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>1.5386832952499001</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>1.5262868404387999</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>1.5276459455489999</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>1.5362294912337999</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>1.5345757007598999</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>1.5257172584534</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>1.5273245573044001</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>1.5236235857010001</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>1.5310940742493</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>1.5277023315430001</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>1.5283534526825</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>1.5168508291245</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>1.5280623435973999</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>1.5220848321914999</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>1.5363885164261</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>1.5163915157318</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>1.5376961231232</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>1.5234137773514</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>1.5224848985671999</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>1.5213706493378001</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>1.5174407958984</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>1.5246992111205999</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>1.5262854099273999</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>1.5158545970916999</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>1.5095905065535999</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>1.5519368648528999</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>1.5412166118621999</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>1.5174753665923999</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>1.5397862195969001</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>1.5159486532211</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>1.5323609113693</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>1.5206880569457999</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>1.5149246454239</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>1.5332043170928999</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>1.5420242547989</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>1.518865942955</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>1.52843105793</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>1.5132231712341</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>1.5239719152450999</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>1.5052651166916</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>1.5118254423141</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>1.5094436407089</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>1.5223784446716</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>1.5144540071487</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>1.5117515325546</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>1.5137788057327</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>1.5073317289352</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>1.5104380846023999</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>1.5060676336287999</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>1.5100166797637999</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>1.5302791595459</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>1.5083832740784</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>1.5374596118927</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>1.5180834531784</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>1.4978188276291</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>1.5198512077332</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>1.4966907501221001</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>1.5067428350448999</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>1.5499503612518</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>1.4968065023421999</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>1.5110614299773999</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>1.4985797405243</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>1.5055221319198999</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>1.5281981229782</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>1.5082385540009</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>1.5109088420868</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>1.5038957595825</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>1.4873013496398999</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>1.5064716339110999</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>1.5095734596252</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>1.4853326082230001</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>1.5012792348862001</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>1.4963634014130001</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>1.4958081245421999</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>1.4953247308730999</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>1.4916917085648</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>1.5062441825866999</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>1.4877541065216</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>1.4907143115996999</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>1.4958342313766</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>1.5281144380569001</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>1.4971783161162999</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>1.4887512922287001</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>1.4894016981125</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>1.4865689277648999</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>1.5035076141357</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>1.4957443475723</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>1.4855179786682</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>1.5007146596909</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>1.4981039762496999</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>1.4871921539307</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>1.4854258298873999</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>1.4911881685257</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>1.4979494810103999</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>1.4977207183837999</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>1.4914437532425</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>1.5000145435333001</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>1.4941965341568</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>1.5020382404327</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>1.4800112247467001</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>1.5049083232880001</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>1.4883879423141</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>1.4931222200394001</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>1.4782942533493</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>1.4917325973511</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>1.4747993946075</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>1.4827216863632</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>1.5005460977553999</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>1.4782894849777</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>1.4804074764252</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>1.4749374389648</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>1.4725537300110001</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>1.4784123897552</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>1.4797154664993</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>1.4759793281555</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>1.4805153608321999</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>1.4846484661102</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>1.5075905323029</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>1.4884043931961</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>1.4897384643555001</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>1.4800490140914999</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>1.4683943986893</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>1.4737371206284</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>1.4919518232346001</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>1.4729743003844999</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>1.4752002954482999</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>1.4791560173035001</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>1.4704324007034</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>1.4988733530045</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>1.4757778644562001</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>1.4769133329391</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>1.4788678884505999</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>1.4702441692352</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>1.4783289432525999</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>1.4632630348205999</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>1.4692748785019001</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>1.4692169427871999</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>1.4786719083786</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>1.4718272686005001</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>1.4842826128005999</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>1.4891296625137</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>1.4713377952575999</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>1.4723830223083001</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>1.4618686437607</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>1.4627724885941</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>1.4769127368927</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>1.4694739580153999</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>1.4749268293380999</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>1.4696115255355999</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>1.4695342779160001</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>1.470085978508</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>1.4739311933517001</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>1.4785389900207999</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>1.4684827327728001</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>1.4646152257919001</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>1.4698261022568</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>1.4660460948944001</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>1.4912949800491</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>1.4652626514435001</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>1.4584201574325999</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>1.4612721204757999</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>1.4631702899932999</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>1.4589450359344001</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>1.4658541679382</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>1.4605312347412001</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>1.4830491542816</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>1.4745160341262999</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>1.4679431915283001</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>1.4710026979446</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>1.4747769832611</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>1.47367811203</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>1.4606310129166</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>1.4709905385971001</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>1.4960359334946001</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>1.4692336320877</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>1.4642307758330999</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>1.4644992351532</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>1.4686814546585001</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>1.4825009107589999</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>1.46759724617</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>1.4669818878173999</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>1.4595932960510001</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>1.4493887424469001</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>1.4933950901030999</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>1.4679323434830001</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>1.4541841745377</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>1.4558613300323</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>1.4601880311966</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>1.4510320425034</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>1.4561158418655</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>1.4546836614609</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>1.4456543922424001</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>1.4533442258835001</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>1.4663755893707</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>1.4542962312698</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>1.4706585407257</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>1.4582281112671001</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>1.4608823060989</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>1.453125</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>1.4614055156707999</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>1.4482828378677</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>1.4754245281219001</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>1.4568212032318</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>1.4543384313583001</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>1.4417662620544001</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>1.4460822343826001</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>1.4658797979355001</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>1.4564709663391</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>1.4536639451980999</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>1.4544109106064</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>1.4420132637023999</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>1.4455878734589001</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>1.4605851173401001</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>1.4427649974823</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>1.4367519617080999</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>1.4548102617264</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>1.4571080207825</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4296-4AF8-B19A-703FFCA3675E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="603335664"/>
+        <c:axId val="609308064"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="603335664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="499"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Epochs</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="609308064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="609308064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Loss</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="603335664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7104,6 +14159,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -7114,10 +15201,10 @@
       <xdr:rowOff>4761</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7140,6 +15227,602 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1240</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>186979</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>8283</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>182219</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF1CA285-DAC7-1D2C-D9E4-D987F3188236}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>186577</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>8283</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{794D4E5E-FA22-3EC0-8CD0-797C0A407868}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>271670</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>23192</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>273326</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>107674</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Retângulo: Cantos Arredondados 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68A5D594-7B93-4CFE-80E8-72FBDF09A241}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13457583" y="8786192"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Validation Loss</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>84483</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>142462</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>115957</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>91108</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Retângulo: Cantos Arredondados 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30AEDE3F-FD98-4A9A-A180-BBB81BB69BFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15109135" y="5857462"/>
+          <a:ext cx="1257300" cy="710646"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Training Loss </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>513521</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>140804</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>99391</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Conector de Seta Reta 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F47BB9F-0D21-E335-68E5-40DEF3B8F88C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="8183217" y="6998804"/>
+          <a:ext cx="480392" cy="530087"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>177248</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>69572</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>372716</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>82825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Conector de Seta Reta 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE3EF5B7-7BBC-4A34-A021-C84B31D7EC11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8459857" y="6356072"/>
+          <a:ext cx="195468" cy="203753"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>225288</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>24848</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>281609</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>51353</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Conector de Seta Reta 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB22060D-E9D8-48B1-836D-BA9B3EC6FBF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="14637027" y="8025848"/>
+          <a:ext cx="669234" cy="788505"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>231913</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>57979</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>125897</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>115957</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Conector de Seta Reta 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EEED26E-9755-4B67-8F8C-1C5EAF2A12F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="14030739" y="6534979"/>
+          <a:ext cx="1119810" cy="1200978"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>233569</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>1658</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>235225</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>86140</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Retângulo: Cantos Arredondados 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{110AE3B2-C195-4788-A014-83F198C03951}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7290352" y="5716658"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Validation Accuracy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>352838</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>62949</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>354494</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>147431</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Retângulo: Cantos Arredondados 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D690B22D-F7F6-4782-A1CF-582E5B0A90FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8635447" y="7492449"/>
+          <a:ext cx="1227482" cy="655982"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600" b="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Training Accuracy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7432,7 +16115,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F504"/>
+  <dimension ref="A1:M501"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -8721,7 +17404,7 @@
         <v>1.6289252042769999</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
@@ -8740,8 +17423,22 @@
       <c r="F65">
         <v>1.6273157596587999</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H65" s="1"/>
+      <c r="I65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
@@ -8760,8 +17457,24 @@
       <c r="F66">
         <v>1.6244364976882999</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I66">
+        <f>AVERAGE(B487:B501)</f>
+        <v>0.86453539927800416</v>
+      </c>
+      <c r="J66">
+        <f>AVERAGE(C487:C501)</f>
+        <v>1.4339271306991535</v>
+      </c>
+      <c r="L66">
+        <f>AVERAGE(E487:E501)</f>
+        <v>0.86925872564315865</v>
+      </c>
+      <c r="M66">
+        <f>AVERAGE(F487:F501)</f>
+        <v>1.4512703498204602</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
@@ -8781,7 +17494,7 @@
         <v>1.6235717535019001</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
@@ -8801,7 +17514,7 @@
         <v>1.6264128684998</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
@@ -8821,7 +17534,7 @@
         <v>1.6238912343979</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
@@ -8841,7 +17554,7 @@
         <v>1.6252491474152</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>69</v>
       </c>
@@ -8861,7 +17574,7 @@
         <v>1.6214674711227</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
@@ -8881,7 +17594,7 @@
         <v>1.6238486766814999</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
@@ -8901,7 +17614,7 @@
         <v>1.6282966136932</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>72</v>
       </c>
@@ -8921,7 +17634,7 @@
         <v>1.6227374076843</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>73</v>
       </c>
@@ -8941,7 +17654,7 @@
         <v>1.6254634857178001</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
@@ -8961,7 +17674,7 @@
         <v>1.6239304542541999</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
@@ -8981,7 +17694,7 @@
         <v>1.6211965084076001</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
@@ -9001,7 +17714,7 @@
         <v>1.6243064403534</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
@@ -9021,7 +17734,7 @@
         <v>1.624107003212</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
@@ -17459,40 +26172,6 @@
       </c>
       <c r="F501">
         <v>1.4571080207825</v>
-      </c>
-    </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A503" s="1"/>
-      <c r="B503" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D503" s="1"/>
-      <c r="E503" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F503" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B504">
-        <f>AVERAGE(B487:B501)</f>
-        <v>0.86453539927800416</v>
-      </c>
-      <c r="C504">
-        <f>AVERAGE(C487:C501)</f>
-        <v>1.4339271306991535</v>
-      </c>
-      <c r="E504">
-        <f>AVERAGE(E487:E501)</f>
-        <v>0.86925872564315865</v>
-      </c>
-      <c r="F504">
-        <f>AVERAGE(F487:F501)</f>
-        <v>1.4512703498204602</v>
       </c>
     </row>
   </sheetData>
